--- a/output/pdf_financials_xlsx/VIPR.xlsx
+++ b/output/pdf_financials_xlsx/VIPR.xlsx
@@ -3722,25 +3722,25 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.545476</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.536812</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.757286</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.793141</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.403712</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.48292</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>10.448754</v>
       </c>
     </row>
     <row r="93">
@@ -6177,7 +6177,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -6930,7 +6934,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -7209,7 +7217,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VIPR.xlsx
+++ b/output/pdf_financials_xlsx/VIPR.xlsx
@@ -810,28 +810,28 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.019003</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.054012</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.023481</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.005431</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000702</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>1.9e-05</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.032589</v>
       </c>
     </row>
     <row r="13">
@@ -1380,28 +1380,28 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.992885</v>
+        <v>-1.011888</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.303621</v>
+        <v>-3.357633</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.923489</v>
+        <v>-1.94697</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-8.205404</v>
+        <v>-8.210834999999999</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.087371</v>
+        <v>-3.088073</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.984691</v>
+        <v>-2.98471</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-2.542735</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-18.300529</v>
+        <v>-18.333118</v>
       </c>
     </row>
     <row r="28">
@@ -1452,28 +1452,28 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.992885</v>
+        <v>-1.011888</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.303621</v>
+        <v>-3.357633</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.921532</v>
+        <v>-1.945013</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-8.181577000000001</v>
+        <v>-8.187008000000001</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.060049</v>
+        <v>-3.060751</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.954128</v>
+        <v>-2.954147</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-2.531712</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-18.296548</v>
+        <v>-18.329137</v>
       </c>
     </row>
     <row r="30">
@@ -1630,25 +1630,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.397766</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>4.305574</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.711902</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.587212</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.588002</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.057438</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.44768</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.407014</v>
@@ -1698,25 +1698,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.397766</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>4.305574</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.711902</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.587212</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.588002</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.057438</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.44768</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.407014</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.39974</v>
+        <v>0.001974</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4.361215</v>
+        <v>0.055641</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.778451</v>
+        <v>0.066549</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.632201</v>
+        <v>0.044989</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.68494</v>
+        <v>0.096938</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.110946</v>
+        <v>0.053508</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.508226</v>
+        <v>0.060546</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.049031</v>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
@@ -13332,7 +13332,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -19578,7 +19578,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">

--- a/output/pdf_financials_xlsx/VIPR.xlsx
+++ b/output/pdf_financials_xlsx/VIPR.xlsx
@@ -4358,22 +4358,22 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.012703</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.008149</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003806</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000203</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003846</v>
       </c>
     </row>
     <row r="112">
@@ -5162,22 +5162,22 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.012703</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.008149</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003806</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000203</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003846</v>
       </c>
     </row>
     <row r="135">
@@ -5196,22 +5196,22 @@
         <v>-2.593672</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-1.907559</v>
+        <v>-1.920262</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-6.984258</v>
+        <v>-6.992407</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-3.123891</v>
+        <v>-3.127697</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-2.977968</v>
+        <v>-2.978171</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-1.996069</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-11.443483</v>
+        <v>-11.447329</v>
       </c>
     </row>
   </sheetData>
@@ -8152,7 +8152,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -10426,7 +10430,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -11468,7 +11476,11 @@
           <t>Acquisition of equipment (Note 4)</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
